--- a/tests/fixtures/reference/production_report.xlsx
+++ b/tests/fixtures/reference/production_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,13 +462,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1000000</v>
+        <v>1040000</v>
       </c>
       <c r="I3" t="n">
-        <v>2602000</v>
+        <v>2762000</v>
       </c>
       <c r="K3" t="n">
-        <v>2602</v>
+        <v>2655.8</v>
       </c>
     </row>
     <row r="4">
@@ -478,13 +478,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1000000</v>
+        <v>1040000</v>
       </c>
       <c r="I4" t="n">
-        <v>2602000</v>
+        <v>2762000</v>
       </c>
       <c r="K4" t="n">
-        <v>2602</v>
+        <v>2655.8</v>
       </c>
     </row>
     <row r="5">
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="I30" t="n">
-        <v>160000</v>
+        <v>320000</v>
       </c>
       <c r="K30" t="n">
         <v>4000</v>
@@ -1139,6 +1139,56 @@
         <v>4000</v>
       </c>
       <c r="K32" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Unit: 63</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G33" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>80000</v>
+      </c>
+      <c r="I33" t="n">
+        <v>80000</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Unit: 69</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>80000</v>
+      </c>
+      <c r="I34" t="n">
+        <v>80000</v>
+      </c>
+      <c r="J34" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K34" t="n">
         <v>4000</v>
       </c>
     </row>
